--- a/all_group_line_df_class.xlsx
+++ b/all_group_line_df_class.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>lineID</t>
+          <t>LineName</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>LineName</t>
+          <t>LineId</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -471,12 +471,14 @@
           <t>FA</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>31</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BSFA02</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BSFA12</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -488,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -496,12 +498,14 @@
           <t>FA</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>33</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BSFA03</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -513,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,12 +525,797 @@
           <t>FA</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>32</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BSFA07</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BSFA08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BSFA09</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BSFA10</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BSFA11</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BSFA12</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>BSFA13</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BSFA14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>IB2FA02</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Runin</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BSRunin01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Runin</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BSRunin03</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Runin</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BSRunin04</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Runin</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BSRunin05</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Runin</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BSRunin06</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Runin</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BSRunin07</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Runin</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BSRunin09</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Runin</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BSRunin10</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BSTesting01</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BSTesting05</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BSTesting06</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BSTesting07</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BSTesting08</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BSTesting09</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BSTesting10</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BSTesting11</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BSTesting12</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BSTesting14</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BSTesting15</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BSTesting16</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>BSTesting17</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
     </row>
